--- a/data/Player_names.xlsx
+++ b/data/Player_names.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\Radical_stats\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\Radical_stats\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E254E22-B619-4445-9C2B-516BBC97DA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/data/Player_names.xlsx
+++ b/data/Player_names.xlsx
@@ -8,35 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\Radical_stats\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E254E22-B619-4445-9C2B-516BBC97DA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655B1373-7042-4D18-B038-6EEF2F4B4717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3087CFCC-9E84-4D6F-A48A-1C34E4905FAE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="37">
+  <si>
+    <t>Player_number</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
   <si>
     <t>02</t>
   </si>
@@ -65,9 +55,6 @@
     <t>240</t>
   </si>
   <si>
-    <t>Rebelión</t>
-  </si>
-  <si>
     <t>26</t>
   </si>
   <si>
@@ -104,10 +91,46 @@
     <t>Patada de mula</t>
   </si>
   <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Player_number</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1013</t>
+  </si>
+  <si>
+    <t>Karma</t>
+  </si>
+  <si>
+    <t>1023</t>
+  </si>
+  <si>
+    <t>Wewe</t>
+  </si>
+  <si>
+    <t>1308</t>
+  </si>
+  <si>
+    <t>Valkiria</t>
+  </si>
+  <si>
+    <t>1920</t>
+  </si>
+  <si>
+    <t>Latina</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Destroy</t>
+  </si>
+  <si>
+    <t>911</t>
+  </si>
+  <si>
+    <t>Comadreja</t>
+  </si>
+  <si>
+    <t>Mamba</t>
   </si>
 </sst>
 </file>
@@ -478,8 +501,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70C83F84-04E6-4A08-A18F-7BECE9D011BE}">
-  <dimension ref="A1:B12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
@@ -488,98 +511,154 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
